--- a/data/trans_bre/IP18E_R1-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18E_R1-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-5,71%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.6033057493507687</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.05637190955630755</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.4770000811745834</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-5.714818647436659</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.006091078575591492</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.0005684662182477289</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.004863900224064904</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.05714818647436659</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,41; 2,22</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-1,6; 2,6</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,28; 3,09</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-31,72; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-3,42; 2,28</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-1,6; 2,67</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-5,32; 3,21</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-31,72; 0,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.412797332722579</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.59708868357384</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.275329376926612</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-31.71975569974964</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.03424307394165552</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.01598469765969808</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.05317025680388338</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.3171975569974964</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.215953457947323</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.596160537806418</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.089311372042557</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.02278377346353542</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.02673837282821757</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.03213667158929936</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-8,42</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-0,21%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-0,71%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-8,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,14; 2,85</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,61; 1,91</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,01; 1,41</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-16,85; -1,42</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-2,22; 3,03</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-2,7; 2,01</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-3,1; 1,48</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-17,26; -1,59</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.1103746447892351</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.2055177850421086</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.6818652925330793</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-8.424391095317251</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.001158130167920608</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.002139460859719981</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.007055055313856902</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.08698248492294676</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,69</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,03</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-3,7%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.138774099178758</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.608633101435123</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.009583584888025</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-16.85396635168141</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.02215152505646659</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.02702353904549235</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.03097544084828836</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1725729329101722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,79; 10,79</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,1; 6,83</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,44; 7,94</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-19,26; 15,72</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-3,27; 13,65</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-5,66; 8,05</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-4,99; 9,54</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-22,17; 23,78</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.846956979183649</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.90635014129483</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.405462081806649</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-1.419274604412613</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.03027433741989706</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.02005994977419298</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.01477330384914159</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>-0.01594857777879404</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,06</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-7,38</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-0,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-7,89%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.689285912292128</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5298569590920787</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.223103115817537</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-3.033138671208147</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.04434856501550764</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.005984507241561914</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.01419782700541456</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.03696386813706878</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,98; 2,8</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,9; 2,18</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 2,02</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-13,42; -0,87</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-2,09; 3,04</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-2,0; 2,34</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-2,22; 2,17</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-14,39; -1,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.788411563189258</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.098080595766293</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.444685886955974</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-19.25755893544488</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.03272529720438008</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.05658385366909239</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.04988528796816647</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2216543512210503</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.79059513356795</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.833126358208603</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.937673410710872</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>15.71637730590115</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1364793872657626</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.08048941769597874</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.0953847908211078</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.2377727181518688</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5348913624521612</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.05850494373765835</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.05993594224862342</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-7.383378255313843</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.005749587721375861</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.0006180756253434716</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.0006368641605210635</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.07889630570803043</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.982436893588927</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.898606201346116</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.108879557455874</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-13.41608214260037</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.02088285951896871</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.01997870000378911</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.02219705650590035</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1438973872452231</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.799356468432311</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.180204614577659</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.024141917181573</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-0.8702447051016832</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.03037398056493946</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.02340548761159309</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.02171610236517124</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>-0.009971739753965045</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
